--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -9,7 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реєстр" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Розподіл розділів" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спірні" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аркуш — Злата" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аркуш — Аліна" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аркуш — Юлія" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спірні" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +33,14 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0033517A"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -79,6 +90,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,15 +457,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -493,7 +506,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>F-70</t>
+          <t>S-10 ↔ GUI-50</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -503,17 +516,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Несуперечливість, п.2 (суперечить іншому документу): F-70 вимагає нагадування «SMS та Viber», але §2.3 зазначає, що у v1.0 немає інтеграції зі SMS-шлюзами й месенджерами.</t>
+          <t>Несуперечливість, п.1-2 (суперечність усередині документа): S-10 «≥8 символів, велика латинська + спецсимвол»; GUI-50 «≥7 символів, 1 цифра, 1 мала літера» — правила пароля несумісні.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>У v1.0 — нагадування всередині системи (сповіщення в кабінеті); SMS/Viber — майбутня версія.</t>
+          <t>Єдине правило: 8-64 символи, ≥1 велика і ≥1 мала латинські, ≥1 цифра, ≥1 спецсимвол; повторити однаково в S-10 і GUI-50.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Злата</t>
+          <t>Аліна, Злата</t>
         </is>
       </c>
     </row>
@@ -523,27 +536,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>F-130</t>
+          <t>F-70 ↔ F-110</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>здійсненність</t>
+          <t>несуперечливість</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Здійсненність (залежить від систем, які продукт не контролює): «вакансія автоматично публікується на всіх провідних порталах вакансій України» суперечить §2.3 (немає інтеграцій).</t>
+          <t>Несуперечливість, п.2 (суперечать одна одній): F-70 «подана заявка зменшує баланс на свою тривалість»; F-110 «Заявки Pending не впливають на баланс до погодження» (а формула F-110 ще й віднімає «дні у заявках, що очікують») — модель балансу суперечлива.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Публікація лише на внутрішній сторінці вакансій; зовнішні портали — майбутнє.</t>
+          <t>Заявка Pending резервує дні (входять у «заплановані»), баланс не зменшується повторно; погодження переводить «заплановані» → «використані».</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Злата</t>
+          <t>Аліна</t>
         </is>
       </c>
     </row>
@@ -553,27 +566,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>F-50</t>
+          <t>F-70 ↔ BL-30</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>здійсненність</t>
+          <t>несуперечливість</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Здійсненність (технологія/зовнішня система): «в реальному часі перевіряє РНОКПП через реєстр ДПС» — інтеграції у v1.0 немає (§2.3).</t>
+          <t>Несуперечливість, п.2: F-70 «тривалість = кількість календарних днів включно»; BL-30 durationDays «кількість робочих днів, суботи й неділі не враховуються» — різна основа обрахунку тривалості відпустки.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>У v1.0 — локальна перевірка формату РНОКПП (10 цифр) через EmployeeValidator.isValidTaxId.</t>
+          <t>Єдина основа: тривалість рахується як durationDays (робочі дні); формулювання F-70 узгодити з BL-30.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Юлія</t>
+          <t>Злата</t>
         </is>
       </c>
     </row>
@@ -583,22 +596,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>S-10 ↔ GUI-50</t>
+          <t>F-50</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>несуперечливість</t>
+          <t>здійсненність</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Несуперечливість, п.1-2: правила пароля суперечать: S-10 «≥8 символів, велика латинська + спецсимвол»; GUI-50 «≥7 символів, цифра + мала літера».</t>
+          <t>Здійсненність (залежить від зовнішньої системи): «в реальному часі перевіряє достовірність РНОКПП через реєстр ДПС» — §2.3: інтеграцій із держреєстрами немає.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Єдине правило: «8-64 символи, щонайменше велика+мала латинські, цифра і спецсимвол»; повторити однаково в S-10 і GUI-50.</t>
+          <t>Локальна перевірка формату РНОКПП (рівно 10 цифр) через EmployeeValidator.isValidTaxId; звірка з ДПС — поза v1.0.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -613,22 +626,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>F-110 ↔ F-70</t>
+          <t>F-90</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>несуперечливість</t>
+          <t>здійсненність</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Несуперечливість, п.2: F-110 «баланс = ліміт − використані − заплановані − дні у заявках, що очікують»; F-70 «подана заявка зменшує баланс» — ризик подвійного віднімання.</t>
+          <t>Здійсненність (залежить від систем, які продукт не контролює): «керівник отримує нагадування SMS та повідомлення у Viber» — §2.3: немає інтеграцій зі SMS-шлюзами й месенджерами.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Заявка у статусі Pending резервує дні (входить у «заплановані»), а не зменшує ліміт двічі.</t>
+          <t>Нагадування в кабінеті системи (внутрішнє сповіщення); SMS/Viber — майбутня версія.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -643,7 +656,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>F-130</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -653,12 +666,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Здійсненність (не залежить лише від системи): «будь-яка сторінка відкривається ≤0,1 с незалежно від каналу зв'язку і кількості записів» — нездійсненно.</t>
+          <t>Здійсненність (зовнішні системи): «автоматично публікується на всіх провідних порталах вакансій України» — §2.3: інтеграцій із порталами вакансій немає.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Поріг серверного часу відповіді ≤0,5 с для 95-го перцентиля за визначених умов.</t>
+          <t>Публікація лише на внутрішній сторінці вакансій продукту; зовнішні портали — майбутнє.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -678,22 +691,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>тестопридатність</t>
+          <t>здійсненність</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Тестопридатність (немає способу спостереження): «незалежно від каналу зв'язку» унеможливлює відтворюваний тест.</t>
+          <t>Здійсненність (не залежить лише від системи): «будь-яка сторінка відкривається ≤0,1 с незалежно від каналу зв'язку і кількості записів» — нездійсненно, час залежить і від каналу.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Переформулювати з умовами вимірювання: середовище, обсяг даних, перцентиль.</t>
+          <t>Поріг серверного часу відповіді ≤0,5 с для 95-го перцентиля за визначених умов (середовище, обсяг даних, канал, інструмент).</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Юлія</t>
+          <t>Злата</t>
         </is>
       </c>
     </row>
@@ -703,27 +716,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>однозначність</t>
+          <t>тестопридатність</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Однозначність, п.4 (єдина інтерпретація): «велику кількість» і «помітної деградації» не визначені.</t>
+          <t>Тестопридатність (немає способу спостереження): «незалежно від каналу зв'язку» унеможливлює відтворюваний вимірюваний тест.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Вказати: 200 одночасних користувачів, зростання часу відповіді ≤20%.</t>
+          <t>Задати умови вимірювання: Docker-резерв 8vCPU/16ГБ, 10 000 працівників / 50 000 заявок, локальна мережа, JMeter, 200 користувачів.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Аліна</t>
+          <t>Юлія</t>
         </is>
       </c>
     </row>
@@ -743,7 +756,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Тестопридатність (слово-маркер «інтуїтивно»): «інтерфейс інтуїтивно зрозумілий, заявка без навчання» — не перевіряється.</t>
+          <t>Тестопридатність (слово-маркер «інтуїтивно»): «інтерфейс інтуїтивно зрозумілий, заявка без навчання» — немає «пройдено / не пройдено».</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -753,7 +766,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Аліна</t>
+          <t>Злата</t>
         </is>
       </c>
     </row>
@@ -773,17 +786,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Тестопридатність (слово-маркер «швидко»): «підсумки оновлюються швидко після зміни» — не вимірюване.</t>
+          <t>Тестопридатність (слово-маркер «швидко»): «підсумки оновлюються швидко після зміни комірки» — не вимірюване.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Оновлення ≤200 мс після зміни комірки.</t>
+          <t>Оновлення ≤200 мс після зміни будь-якої комірки.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Юлія</t>
+          <t>Аліна</t>
         </is>
       </c>
     </row>
@@ -793,27 +806,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>P-20</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>простежуваність</t>
+          <t>однозначність</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Простежуваність, п.? (посилання на неіснуючі вимоги): довідка «для кожної функції F-10 … F-180», а у СВ функції лише до F-140.</t>
+          <t>Однозначність, п.4 (єдина інтерпретація): «велику кількість» і «помітної деградації» не визначені.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Виправити діапазон на F-10…F-140.</t>
+          <t>≥200 одночасних користувачів; зростання середнього часу відповіді ≤20% відносно базового вимірювання за 1 користувача.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Злата</t>
+          <t>Юлія</t>
         </is>
       </c>
     </row>
@@ -823,27 +836,27 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>F-90 (дубль)</t>
+          <t>F-120</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>простежуваність</t>
+          <t>однозначність</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Простежуваність, п.2 (унікальний ID): F-90 присвоєно двом різним вимогам (погодження заявок у Leave List і призначення відпустки Leave→Assign).</t>
+          <t>Однозначність, п.1 (одне значення): не визначено переходи статусів табеля після Rejected (чи редагується, чи новий цикл).</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Перенумерувати другу вимогу вільним ID (F-100); посилання замінити; ID не зсувати.</t>
+          <t>Повний життєвий цикл: Not Submitted → Submitted → Approved/Rejected; після Rejected працівник редагує той самий табель і повторно подає.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Юлія</t>
+          <t>Аліна</t>
         </is>
       </c>
     </row>
@@ -853,27 +866,27 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BL-30</t>
+          <t>F-90 (дубль)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>повнота</t>
+          <t>простежуваність</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Повнота, п.1 (повна інформація): durationDays виключає святкові дні, але джерело переліку святкових днів не визначене.</t>
+          <t>Простежуваність, п.2 (унікальний ID): ID F-90 присвоєно двом різним вимогам (погодження у Leave List і призначення Leave→Assign).</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Додати джерело календаря свят (довідник/конфігурація) і правило оновлення.</t>
+          <t>Другу вимогу (Leave→Assign) перенумерувати на вільний F-100; посилання замінити; інші ID не зсувати.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Аліна</t>
+          <t>Злата</t>
         </is>
       </c>
     </row>
@@ -883,27 +896,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>F-80 / BL-30</t>
+          <t>D-20</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>повнота</t>
+          <t>простежуваність</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Повнота, п.4 (обумовлено всі вхідні дані): для часткових днів (Partial Days) не визначено обрахунок тривалості і балансу.</t>
+          <t>Простежуваність (посилання на неіснуючі вимоги): довідка «для F-10 … F-180», а функції лише до F-140.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Уточнити правило обліку часткових днів у durationDays і балансі (потребує підтвердження замовником).</t>
+          <t>Виправити діапазон на F-10 … F-140.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Злата</t>
+          <t>Юлія</t>
         </is>
       </c>
     </row>
@@ -913,25 +926,55 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>F-120</t>
+          <t>F-70 / BL-30</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>однозначність</t>
+          <t>повнота</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Однозначність, п.1 (одне значення): не визначено переходи статусів табеля після Rejected (чи редагується, чи новий цикл).</t>
+          <t>Повнота, п.4 (обумовлено всі вхідні дані): «за потреби часткові дні» (F-70, GUI-70 Partial Days) — обрахунок тривалості й балансу для часткових днів не визначено.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Описати повний життєвий цикл статусів: Not Submitted → Submitted → Approved/Rejected → (повернення на редагування).</t>
+          <t>Часткові дні — крок 0,5 дня; durationDays додає 0,5 за кожен південь; баланс зменшується на отриману суму (⚠ крок і перелік варіантів Partial Days — підтвердження замовником).</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Злата</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>S-20</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>повнота</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Повнота, п.1 (повна інформація): «сесія завершується після тривалої бездіяльності» — тривалість бездіяльності не задана.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Задати таймаут: автоматичне завершення сесії після 30 хв бездіяльності (значення — параметр конфігурації).</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Юлія</t>
         </is>
@@ -951,7 +994,7 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -976,29 +1019,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1-2. Вступ, загальний опис, терміни</t>
+          <t>1-2. Вступ, загальний опис, терміни, обмеження (§2.3)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>посилання, ролі, обмеження, середовище</t>
+          <t>посилання, ролі, середовище, обмеження (інтеграції)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Аліна</t>
+          <t>Аліна + Злата</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>3. Функціональні вимоги (F-)</t>
+          <t>3. Функціональні вимоги (F-10…F-140)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>F-10…F-140: логіка функцій продукту</t>
+          <t>логіка функцій продукту</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1010,12 +1053,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>4. Вимоги до інтерфейсу (GUI-)</t>
+          <t>4. Вимоги до інтерфейсу (GUI-10…GUI-90)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GUI-10…GUI-90: форми, поля, повідомлення</t>
+          <t>форми, поля, повідомлення, валідація</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1027,12 +1070,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>5. Бізнес-логіка модуля (BL-)</t>
+          <t>5. Бізнес-логіка модуля (BL-10…BL-80)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BL-10…BL-80: правила LeaveCalculator/PayrollCalculator/EmployeeValidator</t>
+          <t>правила LeaveCalculator/PayrollCalculator/EmployeeValidator</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1069,13 +1112,469 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Аудитор: Злата</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Розділи: 3 (F-), 5 (BL-), 6 (нефункц.) + §2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ID вимоги</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Що знайдено (стисло)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>F-70 ↔ BL-30</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>несуперечливість</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Тривалість відпустки: F-70 календарні дні vs BL-30 робочі — розбіжність (перетин §3 і §5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>F-50</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>здійсненність</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>РНОКПП через реєстр ДПС суперечить обмеженню §2.3 «немає інтеграцій».</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>F-130</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>здійсненність</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Публікація на зовнішніх порталах вакансій суперечить §2.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>P-10</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>здійсненність</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>«≤0,1 с незалежно від каналу» — нездійсненний поріг.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>U-20</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>тестопридатність</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>«Інтуїтивно зрозумілий» — немає критерію проходження.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>F-90 (дубль)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>простежуваність</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ID F-90 на двох різних вимогах — порушення унікальності.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>F-70 / BL-30</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>повнота</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Часткові дні згадані, але обрахунок не визначений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S-10 (спільно)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>несуперечливість</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Правило пароля в §6 (S-10) не збігається з §4 (GUI-50).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Аудитор: Аліна</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Розділи: 1-2 (вступ, §2.3), 3 (F-), 4 (GUI-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ID вимоги</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Що знайдено (стисло)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>§2.3 (обмеження)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Звірено перелік заборонених інтеграцій — основа для дефектів F-50, F-90, F-130 (знайдені спільно зі Златою).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>F-70 ↔ F-110</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>несуперечливість</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Баланс: заявка Pending одночасно «зменшує» (F-70) і «не впливає» (F-110).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>F-90</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>здійсненність</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Нагадування SMS/Viber суперечить §2.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GUI-80</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>тестопридатність</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>«Оновлюються швидко» — немає числового порогу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GUI-50 (спільно)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>несуперечливість</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Правило пароля в §4 (GUI-50) не збігається з §6 (S-10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>F-120</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>однозначність</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Переходи статусів табеля після Rejected не описані.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Аудитор: Юлія</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Розділи: 4 (GUI-), 5 (BL-), 6 (нефункц.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ID вимоги</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Що знайдено (стисло)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>P-10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>тестопридатність</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>«Незалежно від каналу зв'язку» — тест невідтворюваний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>P-20</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>однозначність</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>«Велика кількість», «помітна деградація» — без чисел.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>D-20</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>простежуваність</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Довідка посилається на F-180, яких немає (функції до F-140).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>S-20</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>повнота</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Таймаут сесії не заданий («після тривалої бездіяльності»).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1109,7 +1608,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1119,7 +1618,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Переходи статусів після Rejected не описані — тест-кейс на повторне подання неможливо однозначно скласти (тестопридатність/однозначність).</t>
+          <t>Переходи статусів після Rejected не описані — тест-кейс на повторне подання неможливо однозначно скласти.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1130,6 +1629,33 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Прийнято як дефект: «очевидно» не є специфікацією; вимагає явного опису життєвого циклу статусів.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>F-70 ↔ F-110</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Формулювання балансу прямо суперечливі — тест на баланс після подання заявки дасть різні очікувані результати.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Можна здогадатися, що Pending лише «резервує».</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято як дефект: здогад не є вимогою; потрібна єдина однозначна формула балансу.</t>
         </is>
       </c>
     </row>
